--- a/completeness checks/section6b4_discrepancy.xlsx
+++ b/completeness checks/section6b4_discrepancy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="255">
   <si>
     <t xml:space="preserve">hhid</t>
   </si>
@@ -368,6 +368,9 @@
     <t xml:space="preserve">3114-17</t>
   </si>
   <si>
+    <t xml:space="preserve">3115-4</t>
+  </si>
+  <si>
     <t xml:space="preserve">3202-16</t>
   </si>
   <si>
@@ -462,6 +465,9 @@
   </si>
   <si>
     <t xml:space="preserve">3441-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3454-4</t>
   </si>
   <si>
     <t xml:space="preserve">4101-13</t>
@@ -2651,26 +2657,26 @@
       <c r="A116" t="s">
         <v>118</v>
       </c>
-      <c r="B116"/>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
       <c r="C116" t="n">
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>7738</v>
+        <v>11299</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
         <v>119</v>
       </c>
-      <c r="B117" t="n">
-        <v>1</v>
-      </c>
+      <c r="B117"/>
       <c r="C117" t="n">
         <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>4961</v>
+        <v>7738</v>
       </c>
     </row>
     <row r="118">
@@ -2680,9 +2686,11 @@
       <c r="B118" t="n">
         <v>1</v>
       </c>
-      <c r="C118"/>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
       <c r="D118" t="n">
-        <v>5530</v>
+        <v>4961</v>
       </c>
     </row>
     <row r="119">
@@ -2692,23 +2700,23 @@
       <c r="B119" t="n">
         <v>1</v>
       </c>
-      <c r="C119" t="n">
-        <v>1</v>
-      </c>
+      <c r="C119"/>
       <c r="D119" t="n">
-        <v>5169</v>
+        <v>5530</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
         <v>122</v>
       </c>
-      <c r="B120"/>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
       <c r="C120" t="n">
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>5527</v>
+        <v>5169</v>
       </c>
     </row>
     <row r="121">
@@ -2720,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>11219</v>
+        <v>5527</v>
       </c>
     </row>
     <row r="122">
@@ -2732,21 +2740,19 @@
         <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>7705</v>
+        <v>11219</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
         <v>125</v>
       </c>
-      <c r="B123" t="n">
-        <v>1</v>
-      </c>
+      <c r="B123"/>
       <c r="C123" t="n">
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>4508</v>
+        <v>7705</v>
       </c>
     </row>
     <row r="124">
@@ -2760,7 +2766,7 @@
         <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>3972</v>
+        <v>4508</v>
       </c>
     </row>
     <row r="125">
@@ -2774,7 +2780,7 @@
         <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>4070</v>
+        <v>3972</v>
       </c>
     </row>
     <row r="126">
@@ -2785,10 +2791,10 @@
         <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>2652</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="127">
@@ -2799,10 +2805,10 @@
         <v>1</v>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127" t="n">
-        <v>2248</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="128">
@@ -2816,33 +2822,33 @@
         <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>2257</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
         <v>131</v>
       </c>
-      <c r="B129"/>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
       <c r="C129" t="n">
         <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>909</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
         <v>132</v>
       </c>
-      <c r="B130" t="n">
-        <v>1</v>
-      </c>
+      <c r="B130"/>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>920</v>
+        <v>909</v>
       </c>
     </row>
     <row r="131">
@@ -2853,10 +2859,10 @@
         <v>1</v>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D131" t="n">
-        <v>1945</v>
+        <v>920</v>
       </c>
     </row>
     <row r="132">
@@ -2870,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>7814</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="133">
@@ -2884,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>4036</v>
+        <v>7814</v>
       </c>
     </row>
     <row r="134">
@@ -2898,7 +2904,7 @@
         <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>4456</v>
+        <v>4036</v>
       </c>
     </row>
     <row r="135">
@@ -2912,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>11163</v>
+        <v>4456</v>
       </c>
     </row>
     <row r="136">
@@ -2926,7 +2932,7 @@
         <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>11164</v>
+        <v>11163</v>
       </c>
     </row>
     <row r="137">
@@ -2940,19 +2946,21 @@
         <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>1903</v>
+        <v>11164</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
         <v>140</v>
       </c>
-      <c r="B138"/>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
       <c r="C138" t="n">
         <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>7260</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="139">
@@ -2964,7 +2972,7 @@
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>7136</v>
+        <v>7260</v>
       </c>
     </row>
     <row r="140">
@@ -2976,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>11213</v>
+        <v>7136</v>
       </c>
     </row>
     <row r="141">
@@ -2988,21 +2996,19 @@
         <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>11227</v>
+        <v>11213</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
         <v>144</v>
       </c>
-      <c r="B142" t="n">
-        <v>1</v>
-      </c>
+      <c r="B142"/>
       <c r="C142" t="n">
         <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>4108</v>
+        <v>11227</v>
       </c>
     </row>
     <row r="143">
@@ -3016,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>4881</v>
+        <v>4108</v>
       </c>
     </row>
     <row r="144">
@@ -3030,7 +3036,7 @@
         <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>10577</v>
+        <v>4881</v>
       </c>
     </row>
     <row r="145">
@@ -3044,7 +3050,7 @@
         <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>3605</v>
+        <v>10577</v>
       </c>
     </row>
     <row r="146">
@@ -3058,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>10304</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="147">
@@ -3066,25 +3072,27 @@
         <v>149</v>
       </c>
       <c r="B147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>3598</v>
+        <v>10304</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
         <v>150</v>
       </c>
-      <c r="B148"/>
+      <c r="B148" t="n">
+        <v>2</v>
+      </c>
       <c r="C148" t="n">
         <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>4936</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="149">
@@ -3098,19 +3106,19 @@
         <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>5258</v>
+        <v>11381</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
         <v>152</v>
       </c>
-      <c r="B150" t="n">
-        <v>1</v>
-      </c>
-      <c r="C150"/>
+      <c r="B150"/>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
       <c r="D150" t="n">
-        <v>11181</v>
+        <v>4936</v>
       </c>
     </row>
     <row r="151">
@@ -3124,7 +3132,7 @@
         <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>4664</v>
+        <v>5258</v>
       </c>
     </row>
     <row r="152">
@@ -3134,11 +3142,9 @@
       <c r="B152" t="n">
         <v>1</v>
       </c>
-      <c r="C152" t="n">
-        <v>1</v>
-      </c>
+      <c r="C152"/>
       <c r="D152" t="n">
-        <v>4672</v>
+        <v>11181</v>
       </c>
     </row>
     <row r="153">
@@ -3152,7 +3158,7 @@
         <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>4994</v>
+        <v>4664</v>
       </c>
     </row>
     <row r="154">
@@ -3166,7 +3172,7 @@
         <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>11200</v>
+        <v>4672</v>
       </c>
     </row>
     <row r="155">
@@ -3180,19 +3186,21 @@
         <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>2938</v>
+        <v>4994</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
         <v>158</v>
       </c>
-      <c r="B156"/>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
       <c r="C156" t="n">
         <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>841</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="157">
@@ -3206,21 +3214,19 @@
         <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>862</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
         <v>160</v>
       </c>
-      <c r="B158" t="n">
-        <v>1</v>
-      </c>
+      <c r="B158"/>
       <c r="C158" t="n">
         <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>864</v>
+        <v>841</v>
       </c>
     </row>
     <row r="159">
@@ -3234,7 +3240,7 @@
         <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>10914</v>
+        <v>862</v>
       </c>
     </row>
     <row r="160">
@@ -3248,7 +3254,7 @@
         <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>10915</v>
+        <v>864</v>
       </c>
     </row>
     <row r="161">
@@ -3262,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>10911</v>
+        <v>10914</v>
       </c>
     </row>
     <row r="162">
@@ -3276,7 +3282,7 @@
         <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>10761</v>
+        <v>10915</v>
       </c>
     </row>
     <row r="163">
@@ -3290,7 +3296,7 @@
         <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>6813</v>
+        <v>10911</v>
       </c>
     </row>
     <row r="164">
@@ -3304,7 +3310,7 @@
         <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>5777</v>
+        <v>10761</v>
       </c>
     </row>
     <row r="165">
@@ -3318,7 +3324,7 @@
         <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>5834</v>
+        <v>6813</v>
       </c>
     </row>
     <row r="166">
@@ -3332,7 +3338,7 @@
         <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>5108</v>
+        <v>5777</v>
       </c>
     </row>
     <row r="167">
@@ -3346,7 +3352,7 @@
         <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>3037</v>
+        <v>5834</v>
       </c>
     </row>
     <row r="168">
@@ -3360,7 +3366,7 @@
         <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>11186</v>
+        <v>5108</v>
       </c>
     </row>
     <row r="169">
@@ -3374,7 +3380,7 @@
         <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>11287</v>
+        <v>3037</v>
       </c>
     </row>
     <row r="170">
@@ -3388,7 +3394,7 @@
         <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>2940</v>
+        <v>11186</v>
       </c>
     </row>
     <row r="171">
@@ -3402,19 +3408,21 @@
         <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>10952</v>
+        <v>11287</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
         <v>174</v>
       </c>
-      <c r="B172"/>
+      <c r="B172" t="n">
+        <v>1</v>
+      </c>
       <c r="C172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>6494</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="173">
@@ -3428,21 +3436,19 @@
         <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>5022</v>
+        <v>10952</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
         <v>176</v>
       </c>
-      <c r="B174" t="n">
-        <v>1</v>
-      </c>
+      <c r="B174"/>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D174" t="n">
-        <v>6193</v>
+        <v>6494</v>
       </c>
     </row>
     <row r="175">
@@ -3456,71 +3462,73 @@
         <v>1</v>
       </c>
       <c r="D175" t="n">
-        <v>5768</v>
+        <v>5022</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
         <v>178</v>
       </c>
-      <c r="B176"/>
+      <c r="B176" t="n">
+        <v>1</v>
+      </c>
       <c r="C176" t="n">
         <v>1</v>
       </c>
       <c r="D176" t="n">
-        <v>11005</v>
+        <v>6193</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
         <v>179</v>
       </c>
-      <c r="B177"/>
+      <c r="B177" t="n">
+        <v>1</v>
+      </c>
       <c r="C177" t="n">
         <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>2955</v>
+        <v>5768</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
         <v>180</v>
       </c>
-      <c r="B178" t="n">
-        <v>1</v>
-      </c>
+      <c r="B178"/>
       <c r="C178" t="n">
         <v>1</v>
       </c>
       <c r="D178" t="n">
-        <v>8352</v>
+        <v>11005</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
         <v>181</v>
       </c>
-      <c r="B179" t="n">
-        <v>1</v>
-      </c>
+      <c r="B179"/>
       <c r="C179" t="n">
         <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>8321</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
         <v>182</v>
       </c>
-      <c r="B180"/>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
       <c r="C180" t="n">
         <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>2235</v>
+        <v>8352</v>
       </c>
     </row>
     <row r="181">
@@ -3534,7 +3542,7 @@
         <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>750</v>
+        <v>8321</v>
       </c>
     </row>
     <row r="182">
@@ -3543,10 +3551,10 @@
       </c>
       <c r="B182"/>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>752</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="183">
@@ -3560,121 +3568,119 @@
         <v>1</v>
       </c>
       <c r="D183" t="n">
-        <v>889</v>
+        <v>750</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
         <v>186</v>
       </c>
-      <c r="B184" t="n">
-        <v>1</v>
-      </c>
-      <c r="C184"/>
+      <c r="B184"/>
+      <c r="C184" t="n">
+        <v>2</v>
+      </c>
       <c r="D184" t="n">
-        <v>3046</v>
+        <v>752</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
         <v>187</v>
       </c>
-      <c r="B185"/>
+      <c r="B185" t="n">
+        <v>1</v>
+      </c>
       <c r="C185" t="n">
         <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>3198</v>
+        <v>889</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
         <v>188</v>
       </c>
-      <c r="B186"/>
-      <c r="C186" t="n">
-        <v>1</v>
-      </c>
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186"/>
       <c r="D186" t="n">
-        <v>3969</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
         <v>189</v>
       </c>
-      <c r="B187" t="n">
-        <v>2</v>
-      </c>
+      <c r="B187"/>
       <c r="C187" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D187" t="n">
-        <v>4614</v>
+        <v>3198</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
         <v>190</v>
       </c>
-      <c r="B188" t="n">
-        <v>2</v>
-      </c>
-      <c r="C188"/>
+      <c r="B188"/>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
       <c r="D188" t="n">
-        <v>4856</v>
+        <v>3969</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
         <v>191</v>
       </c>
-      <c r="B189"/>
+      <c r="B189" t="n">
+        <v>2</v>
+      </c>
       <c r="C189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D189" t="n">
-        <v>4494</v>
+        <v>4614</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
         <v>192</v>
       </c>
-      <c r="B190"/>
-      <c r="C190" t="n">
-        <v>1</v>
-      </c>
+      <c r="B190" t="n">
+        <v>2</v>
+      </c>
+      <c r="C190"/>
       <c r="D190" t="n">
-        <v>768</v>
+        <v>4856</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
         <v>193</v>
       </c>
-      <c r="B191" t="n">
-        <v>1</v>
-      </c>
+      <c r="B191"/>
       <c r="C191" t="n">
         <v>1</v>
       </c>
       <c r="D191" t="n">
-        <v>3135</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
         <v>194</v>
       </c>
-      <c r="B192" t="n">
-        <v>1</v>
-      </c>
+      <c r="B192"/>
       <c r="C192" t="n">
         <v>1</v>
       </c>
       <c r="D192" t="n">
-        <v>7545</v>
+        <v>768</v>
       </c>
     </row>
     <row r="193">
@@ -3684,59 +3690,61 @@
       <c r="B193" t="n">
         <v>1</v>
       </c>
-      <c r="C193"/>
+      <c r="C193" t="n">
+        <v>1</v>
+      </c>
       <c r="D193" t="n">
-        <v>7548</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
         <v>196</v>
       </c>
-      <c r="B194"/>
+      <c r="B194" t="n">
+        <v>1</v>
+      </c>
       <c r="C194" t="n">
         <v>1</v>
       </c>
       <c r="D194" t="n">
-        <v>7588</v>
+        <v>7545</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
         <v>197</v>
       </c>
-      <c r="B195"/>
-      <c r="C195" t="n">
-        <v>1</v>
-      </c>
+      <c r="B195" t="n">
+        <v>1</v>
+      </c>
+      <c r="C195"/>
       <c r="D195" t="n">
-        <v>7333</v>
+        <v>7548</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
         <v>198</v>
       </c>
-      <c r="B196" t="n">
-        <v>1</v>
-      </c>
+      <c r="B196"/>
       <c r="C196" t="n">
         <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>10798</v>
+        <v>7588</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
         <v>199</v>
       </c>
-      <c r="B197" t="n">
-        <v>1</v>
-      </c>
-      <c r="C197"/>
+      <c r="B197"/>
+      <c r="C197" t="n">
+        <v>1</v>
+      </c>
       <c r="D197" t="n">
-        <v>10799</v>
+        <v>7333</v>
       </c>
     </row>
     <row r="198">
@@ -3750,7 +3758,7 @@
         <v>1</v>
       </c>
       <c r="D198" t="n">
-        <v>10801</v>
+        <v>10798</v>
       </c>
     </row>
     <row r="199">
@@ -3760,11 +3768,9 @@
       <c r="B199" t="n">
         <v>1</v>
       </c>
-      <c r="C199" t="n">
-        <v>1</v>
-      </c>
+      <c r="C199"/>
       <c r="D199" t="n">
-        <v>10802</v>
+        <v>10799</v>
       </c>
     </row>
     <row r="200">
@@ -3774,33 +3780,37 @@
       <c r="B200" t="n">
         <v>1</v>
       </c>
-      <c r="C200"/>
+      <c r="C200" t="n">
+        <v>1</v>
+      </c>
       <c r="D200" t="n">
-        <v>10805</v>
+        <v>10801</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
         <v>203</v>
       </c>
-      <c r="B201"/>
+      <c r="B201" t="n">
+        <v>1</v>
+      </c>
       <c r="C201" t="n">
         <v>1</v>
       </c>
       <c r="D201" t="n">
-        <v>10724</v>
+        <v>10802</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
         <v>204</v>
       </c>
-      <c r="B202"/>
-      <c r="C202" t="n">
-        <v>1</v>
-      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202"/>
       <c r="D202" t="n">
-        <v>10727</v>
+        <v>10805</v>
       </c>
     </row>
     <row r="203">
@@ -3812,35 +3822,31 @@
         <v>1</v>
       </c>
       <c r="D203" t="n">
-        <v>10807</v>
+        <v>10724</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
         <v>206</v>
       </c>
-      <c r="B204" t="n">
-        <v>1</v>
-      </c>
+      <c r="B204"/>
       <c r="C204" t="n">
         <v>1</v>
       </c>
       <c r="D204" t="n">
-        <v>10884</v>
+        <v>10727</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
         <v>207</v>
       </c>
-      <c r="B205" t="n">
-        <v>1</v>
-      </c>
+      <c r="B205"/>
       <c r="C205" t="n">
         <v>1</v>
       </c>
       <c r="D205" t="n">
-        <v>10885</v>
+        <v>10807</v>
       </c>
     </row>
     <row r="206">
@@ -3854,7 +3860,7 @@
         <v>1</v>
       </c>
       <c r="D206" t="n">
-        <v>10886</v>
+        <v>10884</v>
       </c>
     </row>
     <row r="207">
@@ -3868,7 +3874,7 @@
         <v>1</v>
       </c>
       <c r="D207" t="n">
-        <v>10887</v>
+        <v>10885</v>
       </c>
     </row>
     <row r="208">
@@ -3882,19 +3888,21 @@
         <v>1</v>
       </c>
       <c r="D208" t="n">
-        <v>9085</v>
+        <v>10886</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
         <v>211</v>
       </c>
-      <c r="B209"/>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
       <c r="C209" t="n">
         <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>10890</v>
+        <v>10887</v>
       </c>
     </row>
     <row r="210">
@@ -3908,33 +3916,33 @@
         <v>1</v>
       </c>
       <c r="D210" t="n">
-        <v>9135</v>
+        <v>9085</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
         <v>213</v>
       </c>
-      <c r="B211" t="n">
-        <v>1</v>
-      </c>
+      <c r="B211"/>
       <c r="C211" t="n">
         <v>1</v>
       </c>
       <c r="D211" t="n">
-        <v>2221</v>
+        <v>10890</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
         <v>214</v>
       </c>
-      <c r="B212"/>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
       <c r="C212" t="n">
         <v>1</v>
       </c>
       <c r="D212" t="n">
-        <v>2231</v>
+        <v>9135</v>
       </c>
     </row>
     <row r="213">
@@ -3944,33 +3952,35 @@
       <c r="B213" t="n">
         <v>1</v>
       </c>
-      <c r="C213"/>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
       <c r="D213" t="n">
-        <v>3133</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
         <v>216</v>
       </c>
-      <c r="B214" t="n">
-        <v>1</v>
-      </c>
-      <c r="C214"/>
+      <c r="B214"/>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
       <c r="D214" t="n">
-        <v>4713</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
         <v>217</v>
       </c>
-      <c r="B215"/>
-      <c r="C215" t="n">
-        <v>1</v>
-      </c>
+      <c r="B215" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215"/>
       <c r="D215" t="n">
-        <v>4714</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="216">
@@ -3982,21 +3992,19 @@
       </c>
       <c r="C216"/>
       <c r="D216" t="n">
-        <v>4496</v>
+        <v>4713</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
         <v>219</v>
       </c>
-      <c r="B217" t="n">
-        <v>1</v>
-      </c>
+      <c r="B217"/>
       <c r="C217" t="n">
         <v>1</v>
       </c>
       <c r="D217" t="n">
-        <v>1991</v>
+        <v>4714</v>
       </c>
     </row>
     <row r="218">
@@ -4008,19 +4016,21 @@
       </c>
       <c r="C218"/>
       <c r="D218" t="n">
-        <v>7592</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
         <v>221</v>
       </c>
-      <c r="B219"/>
+      <c r="B219" t="n">
+        <v>1</v>
+      </c>
       <c r="C219" t="n">
         <v>1</v>
       </c>
       <c r="D219" t="n">
-        <v>10733</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="220">
@@ -4032,31 +4042,31 @@
       </c>
       <c r="C220"/>
       <c r="D220" t="n">
-        <v>10796</v>
+        <v>7592</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
         <v>223</v>
       </c>
-      <c r="B221" t="n">
-        <v>2</v>
-      </c>
-      <c r="C221"/>
+      <c r="B221"/>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
       <c r="D221" t="n">
-        <v>10797</v>
+        <v>10733</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
         <v>224</v>
       </c>
-      <c r="B222"/>
-      <c r="C222" t="n">
-        <v>1</v>
-      </c>
+      <c r="B222" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222"/>
       <c r="D222" t="n">
-        <v>10809</v>
+        <v>10796</v>
       </c>
     </row>
     <row r="223">
@@ -4064,13 +4074,11 @@
         <v>225</v>
       </c>
       <c r="B223" t="n">
-        <v>1</v>
-      </c>
-      <c r="C223" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C223"/>
       <c r="D223" t="n">
-        <v>5814</v>
+        <v>10797</v>
       </c>
     </row>
     <row r="224">
@@ -4082,33 +4090,33 @@
         <v>1</v>
       </c>
       <c r="D224" t="n">
-        <v>5713</v>
+        <v>10809</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
         <v>227</v>
       </c>
-      <c r="B225"/>
+      <c r="B225" t="n">
+        <v>1</v>
+      </c>
       <c r="C225" t="n">
         <v>1</v>
       </c>
       <c r="D225" t="n">
-        <v>5718</v>
+        <v>5814</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
         <v>228</v>
       </c>
-      <c r="B226" t="n">
-        <v>1</v>
-      </c>
+      <c r="B226"/>
       <c r="C226" t="n">
         <v>1</v>
       </c>
       <c r="D226" t="n">
-        <v>1704</v>
+        <v>5713</v>
       </c>
     </row>
     <row r="227">
@@ -4120,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="D227" t="n">
-        <v>3115</v>
+        <v>5718</v>
       </c>
     </row>
     <row r="228">
@@ -4134,21 +4142,19 @@
         <v>1</v>
       </c>
       <c r="D228" t="n">
-        <v>1682</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
         <v>231</v>
       </c>
-      <c r="B229" t="n">
-        <v>1</v>
-      </c>
+      <c r="B229"/>
       <c r="C229" t="n">
         <v>1</v>
       </c>
       <c r="D229" t="n">
-        <v>4540</v>
+        <v>3115</v>
       </c>
     </row>
     <row r="230">
@@ -4162,7 +4168,7 @@
         <v>1</v>
       </c>
       <c r="D230" t="n">
-        <v>6008</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="231">
@@ -4176,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="D231" t="n">
-        <v>6981</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="232">
@@ -4190,7 +4196,7 @@
         <v>1</v>
       </c>
       <c r="D232" t="n">
-        <v>9375</v>
+        <v>6008</v>
       </c>
     </row>
     <row r="233">
@@ -4204,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>9352</v>
+        <v>6981</v>
       </c>
     </row>
     <row r="234">
@@ -4218,19 +4224,21 @@
         <v>1</v>
       </c>
       <c r="D234" t="n">
-        <v>9372</v>
+        <v>9375</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
         <v>237</v>
       </c>
-      <c r="B235"/>
+      <c r="B235" t="n">
+        <v>1</v>
+      </c>
       <c r="C235" t="n">
         <v>1</v>
       </c>
       <c r="D235" t="n">
-        <v>9395</v>
+        <v>9352</v>
       </c>
     </row>
     <row r="236">
@@ -4244,21 +4252,19 @@
         <v>1</v>
       </c>
       <c r="D236" t="n">
-        <v>9501</v>
+        <v>9372</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
         <v>239</v>
       </c>
-      <c r="B237" t="n">
-        <v>1</v>
-      </c>
+      <c r="B237"/>
       <c r="C237" t="n">
         <v>1</v>
       </c>
       <c r="D237" t="n">
-        <v>10026</v>
+        <v>9395</v>
       </c>
     </row>
     <row r="238">
@@ -4272,7 +4278,7 @@
         <v>1</v>
       </c>
       <c r="D238" t="n">
-        <v>10897</v>
+        <v>9501</v>
       </c>
     </row>
     <row r="239">
@@ -4286,31 +4292,35 @@
         <v>1</v>
       </c>
       <c r="D239" t="n">
-        <v>8478</v>
+        <v>10026</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
         <v>242</v>
       </c>
-      <c r="B240"/>
+      <c r="B240" t="n">
+        <v>1</v>
+      </c>
       <c r="C240" t="n">
         <v>1</v>
       </c>
       <c r="D240" t="n">
-        <v>2595</v>
+        <v>10897</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
         <v>243</v>
       </c>
-      <c r="B241"/>
+      <c r="B241" t="n">
+        <v>1</v>
+      </c>
       <c r="C241" t="n">
         <v>1</v>
       </c>
       <c r="D241" t="n">
-        <v>2607</v>
+        <v>8478</v>
       </c>
     </row>
     <row r="242">
@@ -4322,35 +4332,31 @@
         <v>1</v>
       </c>
       <c r="D242" t="n">
-        <v>2609</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
         <v>245</v>
       </c>
-      <c r="B243" t="n">
-        <v>1</v>
-      </c>
+      <c r="B243"/>
       <c r="C243" t="n">
         <v>1</v>
       </c>
       <c r="D243" t="n">
-        <v>4569</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
         <v>246</v>
       </c>
-      <c r="B244" t="n">
-        <v>1</v>
-      </c>
+      <c r="B244"/>
       <c r="C244" t="n">
         <v>1</v>
       </c>
       <c r="D244" t="n">
-        <v>5223</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="245">
@@ -4360,9 +4366,11 @@
       <c r="B245" t="n">
         <v>1</v>
       </c>
-      <c r="C245"/>
+      <c r="C245" t="n">
+        <v>1</v>
+      </c>
       <c r="D245" t="n">
-        <v>8258</v>
+        <v>4569</v>
       </c>
     </row>
     <row r="246">
@@ -4376,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="D246" t="n">
-        <v>5944</v>
+        <v>5223</v>
       </c>
     </row>
     <row r="247">
@@ -4386,11 +4394,9 @@
       <c r="B247" t="n">
         <v>1</v>
       </c>
-      <c r="C247" t="n">
-        <v>1</v>
-      </c>
+      <c r="C247"/>
       <c r="D247" t="n">
-        <v>6155</v>
+        <v>8258</v>
       </c>
     </row>
     <row r="248">
@@ -4404,7 +4410,7 @@
         <v>1</v>
       </c>
       <c r="D248" t="n">
-        <v>9482</v>
+        <v>5944</v>
       </c>
     </row>
     <row r="249">
@@ -4418,7 +4424,7 @@
         <v>1</v>
       </c>
       <c r="D249" t="n">
-        <v>9498</v>
+        <v>6155</v>
       </c>
     </row>
     <row r="250">
@@ -4432,6 +4438,34 @@
         <v>1</v>
       </c>
       <c r="D250" t="n">
+        <v>9482</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>253</v>
+      </c>
+      <c r="B251" t="n">
+        <v>1</v>
+      </c>
+      <c r="C251" t="n">
+        <v>1</v>
+      </c>
+      <c r="D251" t="n">
+        <v>9498</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>254</v>
+      </c>
+      <c r="B252" t="n">
+        <v>1</v>
+      </c>
+      <c r="C252" t="n">
+        <v>1</v>
+      </c>
+      <c r="D252" t="n">
         <v>8250</v>
       </c>
     </row>
